--- a/Europe_Brent_Spot_Price_FOB.xlsx
+++ b/Europe_Brent_Spot_Price_FOB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinav/Downloads/essentials/projects/uni time sereis project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD2C1EB-DCCA-884B-87DD-50DBA7C4414D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E52BDA9-59AC-7D47-998B-9E792F1BD0A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{772FF280-F015-6042-84B2-4E29C394666F}"/>
+    <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15540" xr2:uid="{A3A6E22B-D637-CD44-9040-3B4B45944619}"/>
   </bookViews>
   <sheets>
     <sheet name="Europe_Brent_Spot_Price_FOB" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>Month</t>
   </si>
   <si>
-    <t>Europe Brent Spot Price FOB Dollars per Barrel</t>
+    <t>Spot_Price</t>
   </si>
 </sst>
 </file>
@@ -886,8 +886,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F06CE0B7-AE17-CD45-9111-41BF6B5708E4}">
-  <dimension ref="A1:B461"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0319A08-DE17-C54F-B7DA-8D9886B243D6}">
+  <dimension ref="A1:B463"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -900,2703 +900,2703 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>45870</v>
+        <v>45931</v>
       </c>
       <c r="B2">
-        <v>67.87</v>
+        <v>64.540000000000006</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>45839</v>
+        <v>45901</v>
       </c>
       <c r="B3">
-        <v>71.040000000000006</v>
+        <v>67.989999999999995</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>45809</v>
+        <v>45870</v>
       </c>
       <c r="B4">
-        <v>71.44</v>
+        <v>67.87</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>45778</v>
+        <v>45839</v>
       </c>
       <c r="B5">
-        <v>64.45</v>
+        <v>71.040000000000006</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>45748</v>
+        <v>45809</v>
       </c>
       <c r="B6">
-        <v>68.13</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>45717</v>
+        <v>45778</v>
       </c>
       <c r="B7">
-        <v>72.73</v>
+        <v>64.45</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>45689</v>
+        <v>45748</v>
       </c>
       <c r="B8">
-        <v>75.44</v>
+        <v>68.13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>45658</v>
+        <v>45717</v>
       </c>
       <c r="B9">
-        <v>79.27</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>45627</v>
+        <v>45689</v>
       </c>
       <c r="B10">
-        <v>73.86</v>
+        <v>75.44</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>45597</v>
+        <v>45658</v>
       </c>
       <c r="B11">
-        <v>74.349999999999994</v>
+        <v>79.27</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>45566</v>
+        <v>45627</v>
       </c>
       <c r="B12">
-        <v>75.63</v>
+        <v>73.86</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>45536</v>
+        <v>45597</v>
       </c>
       <c r="B13">
-        <v>74.02</v>
+        <v>74.349999999999994</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>45505</v>
+        <v>45566</v>
       </c>
       <c r="B14">
-        <v>80.36</v>
+        <v>75.63</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>45474</v>
+        <v>45536</v>
       </c>
       <c r="B15">
-        <v>85.15</v>
+        <v>74.02</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>45444</v>
+        <v>45505</v>
       </c>
       <c r="B16">
-        <v>82.25</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>45413</v>
+        <v>45474</v>
       </c>
       <c r="B17">
-        <v>81.75</v>
+        <v>85.15</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>45383</v>
+        <v>45444</v>
       </c>
       <c r="B18">
-        <v>89.94</v>
+        <v>82.25</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>45352</v>
+        <v>45413</v>
       </c>
       <c r="B19">
-        <v>85.41</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>45323</v>
+        <v>45383</v>
       </c>
       <c r="B20">
-        <v>83.48</v>
+        <v>89.94</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>45292</v>
+        <v>45352</v>
       </c>
       <c r="B21">
-        <v>80.12</v>
+        <v>85.41</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>45261</v>
+        <v>45323</v>
       </c>
       <c r="B22">
-        <v>77.63</v>
+        <v>83.48</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>45231</v>
+        <v>45292</v>
       </c>
       <c r="B23">
-        <v>82.94</v>
+        <v>80.12</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>45200</v>
+        <v>45261</v>
       </c>
       <c r="B24">
-        <v>90.6</v>
+        <v>77.63</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>45170</v>
+        <v>45231</v>
       </c>
       <c r="B25">
-        <v>93.72</v>
+        <v>82.94</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>45139</v>
+        <v>45200</v>
       </c>
       <c r="B26">
-        <v>86.15</v>
+        <v>90.6</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>45108</v>
+        <v>45170</v>
       </c>
       <c r="B27">
-        <v>80.11</v>
+        <v>93.72</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>45078</v>
+        <v>45139</v>
       </c>
       <c r="B28">
-        <v>74.84</v>
+        <v>86.15</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>45047</v>
+        <v>45108</v>
       </c>
       <c r="B29">
-        <v>75.47</v>
+        <v>80.11</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>45017</v>
+        <v>45078</v>
       </c>
       <c r="B30">
-        <v>84.64</v>
+        <v>74.84</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>44986</v>
+        <v>45047</v>
       </c>
       <c r="B31">
-        <v>78.430000000000007</v>
+        <v>75.47</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>44958</v>
+        <v>45017</v>
       </c>
       <c r="B32">
-        <v>82.59</v>
+        <v>84.64</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>44927</v>
+        <v>44986</v>
       </c>
       <c r="B33">
-        <v>82.5</v>
+        <v>78.430000000000007</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>44896</v>
+        <v>44958</v>
       </c>
       <c r="B34">
-        <v>80.92</v>
+        <v>82.59</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>44866</v>
+        <v>44927</v>
       </c>
       <c r="B35">
-        <v>91.42</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
-        <v>44835</v>
+        <v>44896</v>
       </c>
       <c r="B36">
-        <v>93.33</v>
+        <v>80.92</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
-        <v>44805</v>
+        <v>44866</v>
       </c>
       <c r="B37">
-        <v>89.76</v>
+        <v>91.42</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
-        <v>44774</v>
+        <v>44835</v>
       </c>
       <c r="B38">
-        <v>100.45</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
-        <v>44743</v>
+        <v>44805</v>
       </c>
       <c r="B39">
-        <v>111.93</v>
+        <v>89.76</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
-        <v>44713</v>
+        <v>44774</v>
       </c>
       <c r="B40">
-        <v>122.71</v>
+        <v>100.45</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
-        <v>44682</v>
+        <v>44743</v>
       </c>
       <c r="B41">
-        <v>113.34</v>
+        <v>111.93</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
-        <v>44652</v>
+        <v>44713</v>
       </c>
       <c r="B42">
-        <v>104.58</v>
+        <v>122.71</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
-        <v>44621</v>
+        <v>44682</v>
       </c>
       <c r="B43">
-        <v>117.25</v>
+        <v>113.34</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
-        <v>44593</v>
+        <v>44652</v>
       </c>
       <c r="B44">
-        <v>97.13</v>
+        <v>104.58</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
-        <v>44562</v>
+        <v>44621</v>
       </c>
       <c r="B45">
-        <v>86.51</v>
+        <v>117.25</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
-        <v>44531</v>
+        <v>44593</v>
       </c>
       <c r="B46">
-        <v>74.17</v>
+        <v>97.13</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
-        <v>44501</v>
+        <v>44562</v>
       </c>
       <c r="B47">
-        <v>81.05</v>
+        <v>86.51</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
-        <v>44470</v>
+        <v>44531</v>
       </c>
       <c r="B48">
-        <v>83.54</v>
+        <v>74.17</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
-        <v>44440</v>
+        <v>44501</v>
       </c>
       <c r="B49">
-        <v>74.489999999999995</v>
+        <v>81.05</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
-        <v>44409</v>
+        <v>44470</v>
       </c>
       <c r="B50">
-        <v>70.75</v>
+        <v>83.54</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
-        <v>44378</v>
+        <v>44440</v>
       </c>
       <c r="B51">
-        <v>75.17</v>
+        <v>74.489999999999995</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
-        <v>44348</v>
+        <v>44409</v>
       </c>
       <c r="B52">
-        <v>73.16</v>
+        <v>70.75</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
-        <v>44317</v>
+        <v>44378</v>
       </c>
       <c r="B53">
-        <v>68.53</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
-        <v>44287</v>
+        <v>44348</v>
       </c>
       <c r="B54">
-        <v>64.81</v>
+        <v>73.16</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
-        <v>44256</v>
+        <v>44317</v>
       </c>
       <c r="B55">
-        <v>65.41</v>
+        <v>68.53</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
-        <v>44228</v>
+        <v>44287</v>
       </c>
       <c r="B56">
-        <v>62.28</v>
+        <v>64.81</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
-        <v>44197</v>
+        <v>44256</v>
       </c>
       <c r="B57">
-        <v>54.77</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
-        <v>44166</v>
+        <v>44228</v>
       </c>
       <c r="B58">
-        <v>49.99</v>
+        <v>62.28</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
-        <v>44136</v>
+        <v>44197</v>
       </c>
       <c r="B59">
-        <v>42.69</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
-        <v>44105</v>
+        <v>44166</v>
       </c>
       <c r="B60">
-        <v>40.19</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
-        <v>44075</v>
+        <v>44136</v>
       </c>
       <c r="B61">
-        <v>40.909999999999997</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
-        <v>44044</v>
+        <v>44105</v>
       </c>
       <c r="B62">
-        <v>44.74</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
-        <v>44013</v>
+        <v>44075</v>
       </c>
       <c r="B63">
-        <v>43.24</v>
+        <v>40.909999999999997</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
-        <v>43983</v>
+        <v>44044</v>
       </c>
       <c r="B64">
-        <v>40.270000000000003</v>
+        <v>44.74</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
-        <v>43952</v>
+        <v>44013</v>
       </c>
       <c r="B65">
-        <v>29.38</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
-        <v>43922</v>
+        <v>43983</v>
       </c>
       <c r="B66">
-        <v>18.38</v>
+        <v>40.270000000000003</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
-        <v>43891</v>
+        <v>43952</v>
       </c>
       <c r="B67">
-        <v>32.01</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
-        <v>43862</v>
+        <v>43922</v>
       </c>
       <c r="B68">
-        <v>55.66</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="B69">
-        <v>63.65</v>
+        <v>32.01</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
-        <v>43800</v>
+        <v>43862</v>
       </c>
       <c r="B70">
-        <v>67.31</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
-        <v>43770</v>
+        <v>43831</v>
       </c>
       <c r="B71">
-        <v>63.21</v>
+        <v>63.65</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
-        <v>43739</v>
+        <v>43800</v>
       </c>
       <c r="B72">
-        <v>59.71</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
-        <v>43709</v>
+        <v>43770</v>
       </c>
       <c r="B73">
-        <v>62.83</v>
+        <v>63.21</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
-        <v>43678</v>
+        <v>43739</v>
       </c>
       <c r="B74">
-        <v>59.04</v>
+        <v>59.71</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
-        <v>43647</v>
+        <v>43709</v>
       </c>
       <c r="B75">
-        <v>63.92</v>
+        <v>62.83</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
-        <v>43617</v>
+        <v>43678</v>
       </c>
       <c r="B76">
-        <v>64.22</v>
+        <v>59.04</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
-        <v>43586</v>
+        <v>43647</v>
       </c>
       <c r="B77">
-        <v>71.319999999999993</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
-        <v>43556</v>
+        <v>43617</v>
       </c>
       <c r="B78">
-        <v>71.23</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
-        <v>43525</v>
+        <v>43586</v>
       </c>
       <c r="B79">
-        <v>66.14</v>
+        <v>71.319999999999993</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
-        <v>43497</v>
+        <v>43556</v>
       </c>
       <c r="B80">
-        <v>63.96</v>
+        <v>71.23</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
-        <v>43466</v>
+        <v>43525</v>
       </c>
       <c r="B81">
-        <v>59.41</v>
+        <v>66.14</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
-        <v>43435</v>
+        <v>43497</v>
       </c>
       <c r="B82">
-        <v>57.36</v>
+        <v>63.96</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
-        <v>43405</v>
+        <v>43466</v>
       </c>
       <c r="B83">
-        <v>64.75</v>
+        <v>59.41</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
-        <v>43374</v>
+        <v>43435</v>
       </c>
       <c r="B84">
-        <v>81.03</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
-        <v>43344</v>
+        <v>43405</v>
       </c>
       <c r="B85">
-        <v>78.89</v>
+        <v>64.75</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
-        <v>43313</v>
+        <v>43374</v>
       </c>
       <c r="B86">
-        <v>72.53</v>
+        <v>81.03</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
-        <v>43282</v>
+        <v>43344</v>
       </c>
       <c r="B87">
-        <v>74.25</v>
+        <v>78.89</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
-        <v>43252</v>
+        <v>43313</v>
       </c>
       <c r="B88">
-        <v>74.41</v>
+        <v>72.53</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
-        <v>43221</v>
+        <v>43282</v>
       </c>
       <c r="B89">
-        <v>76.98</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
-        <v>43191</v>
+        <v>43252</v>
       </c>
       <c r="B90">
-        <v>72.11</v>
+        <v>74.41</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
-        <v>43160</v>
+        <v>43221</v>
       </c>
       <c r="B91">
-        <v>66.02</v>
+        <v>76.98</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
-        <v>43132</v>
+        <v>43191</v>
       </c>
       <c r="B92">
-        <v>65.319999999999993</v>
+        <v>72.11</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
-        <v>43101</v>
+        <v>43160</v>
       </c>
       <c r="B93">
-        <v>69.08</v>
+        <v>66.02</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
-        <v>43070</v>
+        <v>43132</v>
       </c>
       <c r="B94">
-        <v>64.37</v>
+        <v>65.319999999999993</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
-        <v>43040</v>
+        <v>43101</v>
       </c>
       <c r="B95">
-        <v>62.71</v>
+        <v>69.08</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
-        <v>43009</v>
+        <v>43070</v>
       </c>
       <c r="B96">
-        <v>57.51</v>
+        <v>64.37</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
-        <v>42979</v>
+        <v>43040</v>
       </c>
       <c r="B97">
-        <v>56.15</v>
+        <v>62.71</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
-        <v>42948</v>
+        <v>43009</v>
       </c>
       <c r="B98">
-        <v>51.7</v>
+        <v>57.51</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
-        <v>42917</v>
+        <v>42979</v>
       </c>
       <c r="B99">
-        <v>48.48</v>
+        <v>56.15</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
-        <v>42887</v>
+        <v>42948</v>
       </c>
       <c r="B100">
-        <v>46.37</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
-        <v>42856</v>
+        <v>42917</v>
       </c>
       <c r="B101">
-        <v>50.33</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
-        <v>42826</v>
+        <v>42887</v>
       </c>
       <c r="B102">
-        <v>52.31</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
-        <v>42795</v>
+        <v>42856</v>
       </c>
       <c r="B103">
-        <v>51.59</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
-        <v>42767</v>
+        <v>42826</v>
       </c>
       <c r="B104">
-        <v>54.87</v>
+        <v>52.31</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
-        <v>42736</v>
+        <v>42795</v>
       </c>
       <c r="B105">
-        <v>54.58</v>
+        <v>51.59</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
-        <v>42705</v>
+        <v>42767</v>
       </c>
       <c r="B106">
-        <v>53.31</v>
+        <v>54.87</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
-        <v>42675</v>
+        <v>42736</v>
       </c>
       <c r="B107">
-        <v>44.73</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
-        <v>42644</v>
+        <v>42705</v>
       </c>
       <c r="B108">
-        <v>49.52</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
-        <v>42614</v>
+        <v>42675</v>
       </c>
       <c r="B109">
-        <v>46.57</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
-        <v>42583</v>
+        <v>42644</v>
       </c>
       <c r="B110">
-        <v>45.84</v>
+        <v>49.52</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
-        <v>42552</v>
+        <v>42614</v>
       </c>
       <c r="B111">
-        <v>44.95</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
-        <v>42522</v>
+        <v>42583</v>
       </c>
       <c r="B112">
-        <v>48.25</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
-        <v>42491</v>
+        <v>42552</v>
       </c>
       <c r="B113">
-        <v>46.74</v>
+        <v>44.95</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
-        <v>42461</v>
+        <v>42522</v>
       </c>
       <c r="B114">
-        <v>41.58</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
-        <v>42430</v>
+        <v>42491</v>
       </c>
       <c r="B115">
-        <v>38.21</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
-        <v>42401</v>
+        <v>42461</v>
       </c>
       <c r="B116">
-        <v>32.18</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
-        <v>42370</v>
+        <v>42430</v>
       </c>
       <c r="B117">
-        <v>30.7</v>
+        <v>38.21</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
-        <v>42339</v>
+        <v>42401</v>
       </c>
       <c r="B118">
-        <v>38.01</v>
+        <v>32.18</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
-        <v>42309</v>
+        <v>42370</v>
       </c>
       <c r="B119">
-        <v>44.27</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
-        <v>42278</v>
+        <v>42339</v>
       </c>
       <c r="B120">
-        <v>48.43</v>
+        <v>38.01</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
-        <v>42248</v>
+        <v>42309</v>
       </c>
       <c r="B121">
-        <v>47.62</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
-        <v>42217</v>
+        <v>42278</v>
       </c>
       <c r="B122">
-        <v>46.52</v>
+        <v>48.43</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
-        <v>42186</v>
+        <v>42248</v>
       </c>
       <c r="B123">
-        <v>56.56</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
-        <v>42156</v>
+        <v>42217</v>
       </c>
       <c r="B124">
-        <v>61.48</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
-        <v>42125</v>
+        <v>42186</v>
       </c>
       <c r="B125">
-        <v>64.08</v>
+        <v>56.56</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
-        <v>42095</v>
+        <v>42156</v>
       </c>
       <c r="B126">
-        <v>59.52</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
-        <v>42064</v>
+        <v>42125</v>
       </c>
       <c r="B127">
-        <v>55.89</v>
+        <v>64.08</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
-        <v>42036</v>
+        <v>42095</v>
       </c>
       <c r="B128">
-        <v>58.1</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
-        <v>42005</v>
+        <v>42064</v>
       </c>
       <c r="B129">
-        <v>47.76</v>
+        <v>55.89</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
-        <v>41974</v>
+        <v>42036</v>
       </c>
       <c r="B130">
-        <v>62.34</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
-        <v>41944</v>
+        <v>42005</v>
       </c>
       <c r="B131">
-        <v>79.44</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
-        <v>41913</v>
+        <v>41974</v>
       </c>
       <c r="B132">
-        <v>87.43</v>
+        <v>62.34</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
-        <v>41883</v>
+        <v>41944</v>
       </c>
       <c r="B133">
-        <v>97.09</v>
+        <v>79.44</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
-        <v>41852</v>
+        <v>41913</v>
       </c>
       <c r="B134">
-        <v>101.61</v>
+        <v>87.43</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
-        <v>41821</v>
+        <v>41883</v>
       </c>
       <c r="B135">
-        <v>106.77</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
-        <v>41791</v>
+        <v>41852</v>
       </c>
       <c r="B136">
-        <v>111.8</v>
+        <v>101.61</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
-        <v>41760</v>
+        <v>41821</v>
       </c>
       <c r="B137">
-        <v>109.54</v>
+        <v>106.77</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
-        <v>41730</v>
+        <v>41791</v>
       </c>
       <c r="B138">
-        <v>107.76</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
-        <v>41699</v>
+        <v>41760</v>
       </c>
       <c r="B139">
-        <v>107.48</v>
+        <v>109.54</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
-        <v>41671</v>
+        <v>41730</v>
       </c>
       <c r="B140">
-        <v>108.9</v>
+        <v>107.76</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
-        <v>41640</v>
+        <v>41699</v>
       </c>
       <c r="B141">
-        <v>108.12</v>
+        <v>107.48</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
-        <v>41609</v>
+        <v>41671</v>
       </c>
       <c r="B142">
-        <v>110.76</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
-        <v>41579</v>
+        <v>41640</v>
       </c>
       <c r="B143">
-        <v>107.79</v>
+        <v>108.12</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
-        <v>41548</v>
+        <v>41609</v>
       </c>
       <c r="B144">
-        <v>109.08</v>
+        <v>110.76</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
-        <v>41518</v>
+        <v>41579</v>
       </c>
       <c r="B145">
-        <v>111.6</v>
+        <v>107.79</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
-        <v>41487</v>
+        <v>41548</v>
       </c>
       <c r="B146">
-        <v>111.28</v>
+        <v>109.08</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
-        <v>41456</v>
+        <v>41518</v>
       </c>
       <c r="B147">
-        <v>107.93</v>
+        <v>111.6</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
-        <v>41426</v>
+        <v>41487</v>
       </c>
       <c r="B148">
-        <v>102.92</v>
+        <v>111.28</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
-        <v>41395</v>
+        <v>41456</v>
       </c>
       <c r="B149">
-        <v>102.56</v>
+        <v>107.93</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
-        <v>41365</v>
+        <v>41426</v>
       </c>
       <c r="B150">
-        <v>102.25</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
-        <v>41334</v>
+        <v>41395</v>
       </c>
       <c r="B151">
-        <v>108.47</v>
+        <v>102.56</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
-        <v>41306</v>
+        <v>41365</v>
       </c>
       <c r="B152">
-        <v>116.05</v>
+        <v>102.25</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
-        <v>41275</v>
+        <v>41334</v>
       </c>
       <c r="B153">
-        <v>112.96</v>
+        <v>108.47</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
-        <v>41244</v>
+        <v>41306</v>
       </c>
       <c r="B154">
-        <v>109.49</v>
+        <v>116.05</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
-        <v>41214</v>
+        <v>41275</v>
       </c>
       <c r="B155">
-        <v>109.06</v>
+        <v>112.96</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
-        <v>41183</v>
+        <v>41244</v>
       </c>
       <c r="B156">
-        <v>111.71</v>
+        <v>109.49</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
-        <v>41153</v>
+        <v>41214</v>
       </c>
       <c r="B157">
-        <v>112.86</v>
+        <v>109.06</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
-        <v>41122</v>
+        <v>41183</v>
       </c>
       <c r="B158">
-        <v>113.36</v>
+        <v>111.71</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
-        <v>41091</v>
+        <v>41153</v>
       </c>
       <c r="B159">
-        <v>102.62</v>
+        <v>112.86</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
-        <v>41061</v>
+        <v>41122</v>
       </c>
       <c r="B160">
-        <v>95.16</v>
+        <v>113.36</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
-        <v>41030</v>
+        <v>41091</v>
       </c>
       <c r="B161">
-        <v>110.34</v>
+        <v>102.62</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
-        <v>41000</v>
+        <v>41061</v>
       </c>
       <c r="B162">
-        <v>119.75</v>
+        <v>95.16</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
-        <v>40969</v>
+        <v>41030</v>
       </c>
       <c r="B163">
-        <v>125.45</v>
+        <v>110.34</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
-        <v>40940</v>
+        <v>41000</v>
       </c>
       <c r="B164">
-        <v>119.33</v>
+        <v>119.75</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
-        <v>40909</v>
+        <v>40969</v>
       </c>
       <c r="B165">
-        <v>110.69</v>
+        <v>125.45</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
-        <v>40878</v>
+        <v>40940</v>
       </c>
       <c r="B166">
-        <v>107.87</v>
+        <v>119.33</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
-        <v>40848</v>
+        <v>40909</v>
       </c>
       <c r="B167">
-        <v>110.77</v>
+        <v>110.69</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
-        <v>40817</v>
+        <v>40878</v>
       </c>
       <c r="B168">
-        <v>109.55</v>
+        <v>107.87</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
-        <v>40787</v>
+        <v>40848</v>
       </c>
       <c r="B169">
-        <v>112.83</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
-        <v>40756</v>
+        <v>40817</v>
       </c>
       <c r="B170">
-        <v>110.22</v>
+        <v>109.55</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
-        <v>40725</v>
+        <v>40787</v>
       </c>
       <c r="B171">
-        <v>116.97</v>
+        <v>112.83</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
-        <v>40695</v>
+        <v>40756</v>
       </c>
       <c r="B172">
-        <v>113.83</v>
+        <v>110.22</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
-        <v>40664</v>
+        <v>40725</v>
       </c>
       <c r="B173">
-        <v>114.99</v>
+        <v>116.97</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
-        <v>40634</v>
+        <v>40695</v>
       </c>
       <c r="B174">
-        <v>123.26</v>
+        <v>113.83</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
-        <v>40603</v>
+        <v>40664</v>
       </c>
       <c r="B175">
-        <v>114.64</v>
+        <v>114.99</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
-        <v>40575</v>
+        <v>40634</v>
       </c>
       <c r="B176">
-        <v>103.72</v>
+        <v>123.26</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
-        <v>40544</v>
+        <v>40603</v>
       </c>
       <c r="B177">
-        <v>96.52</v>
+        <v>114.64</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
-        <v>40513</v>
+        <v>40575</v>
       </c>
       <c r="B178">
-        <v>91.45</v>
+        <v>103.72</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
-        <v>40483</v>
+        <v>40544</v>
       </c>
       <c r="B179">
-        <v>85.28</v>
+        <v>96.52</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
-        <v>40452</v>
+        <v>40513</v>
       </c>
       <c r="B180">
-        <v>82.67</v>
+        <v>91.45</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
-        <v>40422</v>
+        <v>40483</v>
       </c>
       <c r="B181">
-        <v>77.84</v>
+        <v>85.28</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
-        <v>40391</v>
+        <v>40452</v>
       </c>
       <c r="B182">
-        <v>77.040000000000006</v>
+        <v>82.67</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
-        <v>40360</v>
+        <v>40422</v>
       </c>
       <c r="B183">
-        <v>75.58</v>
+        <v>77.84</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
-        <v>40330</v>
+        <v>40391</v>
       </c>
       <c r="B184">
-        <v>74.760000000000005</v>
+        <v>77.040000000000006</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
-        <v>40299</v>
+        <v>40360</v>
       </c>
       <c r="B185">
-        <v>75.95</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
-        <v>40269</v>
+        <v>40330</v>
       </c>
       <c r="B186">
-        <v>84.82</v>
+        <v>74.760000000000005</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
-        <v>40238</v>
+        <v>40299</v>
       </c>
       <c r="B187">
-        <v>78.83</v>
+        <v>75.95</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
-        <v>40210</v>
+        <v>40269</v>
       </c>
       <c r="B188">
-        <v>73.75</v>
+        <v>84.82</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
-        <v>40179</v>
+        <v>40238</v>
       </c>
       <c r="B189">
-        <v>76.17</v>
+        <v>78.83</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
-        <v>40148</v>
+        <v>40210</v>
       </c>
       <c r="B190">
-        <v>74.459999999999994</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
-        <v>40118</v>
+        <v>40179</v>
       </c>
       <c r="B191">
-        <v>76.66</v>
+        <v>76.17</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
-        <v>40087</v>
+        <v>40148</v>
       </c>
       <c r="B192">
-        <v>72.77</v>
+        <v>74.459999999999994</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
-        <v>40057</v>
+        <v>40118</v>
       </c>
       <c r="B193">
-        <v>67.650000000000006</v>
+        <v>76.66</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
-        <v>40026</v>
+        <v>40087</v>
       </c>
       <c r="B194">
-        <v>72.510000000000005</v>
+        <v>72.77</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
-        <v>39995</v>
+        <v>40057</v>
       </c>
       <c r="B195">
-        <v>64.44</v>
+        <v>67.650000000000006</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
-        <v>39965</v>
+        <v>40026</v>
       </c>
       <c r="B196">
-        <v>68.61</v>
+        <v>72.510000000000005</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
-        <v>39934</v>
+        <v>39995</v>
       </c>
       <c r="B197">
-        <v>57.3</v>
+        <v>64.44</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
-        <v>39904</v>
+        <v>39965</v>
       </c>
       <c r="B198">
-        <v>50.18</v>
+        <v>68.61</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
-        <v>39873</v>
+        <v>39934</v>
       </c>
       <c r="B199">
-        <v>46.54</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
-        <v>39845</v>
+        <v>39904</v>
       </c>
       <c r="B200">
-        <v>43.32</v>
+        <v>50.18</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
-        <v>39814</v>
+        <v>39873</v>
       </c>
       <c r="B201">
-        <v>43.44</v>
+        <v>46.54</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
-        <v>39783</v>
+        <v>39845</v>
       </c>
       <c r="B202">
-        <v>39.950000000000003</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
-        <v>39753</v>
+        <v>39814</v>
       </c>
       <c r="B203">
-        <v>52.45</v>
+        <v>43.44</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
-        <v>39722</v>
+        <v>39783</v>
       </c>
       <c r="B204">
-        <v>71.58</v>
+        <v>39.950000000000003</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
-        <v>39692</v>
+        <v>39753</v>
       </c>
       <c r="B205">
-        <v>97.23</v>
+        <v>52.45</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
-        <v>39661</v>
+        <v>39722</v>
       </c>
       <c r="B206">
-        <v>113.24</v>
+        <v>71.58</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
-        <v>39630</v>
+        <v>39692</v>
       </c>
       <c r="B207">
-        <v>132.72</v>
+        <v>97.23</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
-        <v>39600</v>
+        <v>39661</v>
       </c>
       <c r="B208">
-        <v>132.32</v>
+        <v>113.24</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
-        <v>39569</v>
+        <v>39630</v>
       </c>
       <c r="B209">
-        <v>122.8</v>
+        <v>132.72</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
-        <v>39539</v>
+        <v>39600</v>
       </c>
       <c r="B210">
-        <v>109.07</v>
+        <v>132.32</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
-        <v>39508</v>
+        <v>39569</v>
       </c>
       <c r="B211">
-        <v>103.64</v>
+        <v>122.8</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
-        <v>39479</v>
+        <v>39539</v>
       </c>
       <c r="B212">
-        <v>94.99</v>
+        <v>109.07</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
-        <v>39448</v>
+        <v>39508</v>
       </c>
       <c r="B213">
-        <v>92.18</v>
+        <v>103.64</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
-        <v>39417</v>
+        <v>39479</v>
       </c>
       <c r="B214">
-        <v>90.93</v>
+        <v>94.99</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
-        <v>39387</v>
+        <v>39448</v>
       </c>
       <c r="B215">
-        <v>92.41</v>
+        <v>92.18</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
-        <v>39356</v>
+        <v>39417</v>
       </c>
       <c r="B216">
-        <v>82.34</v>
+        <v>90.93</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
-        <v>39326</v>
+        <v>39387</v>
       </c>
       <c r="B217">
-        <v>77.17</v>
+        <v>92.41</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
-        <v>39295</v>
+        <v>39356</v>
       </c>
       <c r="B218">
-        <v>70.760000000000005</v>
+        <v>82.34</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
-        <v>39264</v>
+        <v>39326</v>
       </c>
       <c r="B219">
-        <v>76.930000000000007</v>
+        <v>77.17</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
-        <v>39234</v>
+        <v>39295</v>
       </c>
       <c r="B220">
-        <v>71.05</v>
+        <v>70.760000000000005</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
-        <v>39203</v>
+        <v>39264</v>
       </c>
       <c r="B221">
-        <v>67.209999999999994</v>
+        <v>76.930000000000007</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
-        <v>39173</v>
+        <v>39234</v>
       </c>
       <c r="B222">
-        <v>67.489999999999995</v>
+        <v>71.05</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
-        <v>39142</v>
+        <v>39203</v>
       </c>
       <c r="B223">
-        <v>62.05</v>
+        <v>67.209999999999994</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
-        <v>39114</v>
+        <v>39173</v>
       </c>
       <c r="B224">
-        <v>57.56</v>
+        <v>67.489999999999995</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
-        <v>39083</v>
+        <v>39142</v>
       </c>
       <c r="B225">
-        <v>53.68</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
-        <v>39052</v>
+        <v>39114</v>
       </c>
       <c r="B226">
-        <v>62.47</v>
+        <v>57.56</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
-        <v>39022</v>
+        <v>39083</v>
       </c>
       <c r="B227">
-        <v>58.76</v>
+        <v>53.68</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
-        <v>38991</v>
+        <v>39052</v>
       </c>
       <c r="B228">
-        <v>57.81</v>
+        <v>62.47</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
-        <v>38961</v>
+        <v>39022</v>
       </c>
       <c r="B229">
-        <v>61.96</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
-        <v>38930</v>
+        <v>38991</v>
       </c>
       <c r="B230">
-        <v>73.23</v>
+        <v>57.81</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
-        <v>38899</v>
+        <v>38961</v>
       </c>
       <c r="B231">
-        <v>73.67</v>
+        <v>61.96</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
-        <v>38869</v>
+        <v>38930</v>
       </c>
       <c r="B232">
-        <v>68.56</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
-        <v>38838</v>
+        <v>38899</v>
       </c>
       <c r="B233">
-        <v>69.78</v>
+        <v>73.67</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
-        <v>38808</v>
+        <v>38869</v>
       </c>
       <c r="B234">
-        <v>70.260000000000005</v>
+        <v>68.56</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
-        <v>38777</v>
+        <v>38838</v>
       </c>
       <c r="B235">
-        <v>62.06</v>
+        <v>69.78</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
-        <v>38749</v>
+        <v>38808</v>
       </c>
       <c r="B236">
-        <v>60.21</v>
+        <v>70.260000000000005</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
-        <v>38718</v>
+        <v>38777</v>
       </c>
       <c r="B237">
-        <v>62.99</v>
+        <v>62.06</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
-        <v>38687</v>
+        <v>38749</v>
       </c>
       <c r="B238">
-        <v>56.86</v>
+        <v>60.21</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
-        <v>38657</v>
+        <v>38718</v>
       </c>
       <c r="B239">
-        <v>55.24</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
-        <v>38626</v>
+        <v>38687</v>
       </c>
       <c r="B240">
-        <v>58.54</v>
+        <v>56.86</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
-        <v>38596</v>
+        <v>38657</v>
       </c>
       <c r="B241">
-        <v>62.91</v>
+        <v>55.24</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
-        <v>38565</v>
+        <v>38626</v>
       </c>
       <c r="B242">
-        <v>63.98</v>
+        <v>58.54</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
-        <v>38534</v>
+        <v>38596</v>
       </c>
       <c r="B243">
-        <v>57.52</v>
+        <v>62.91</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
-        <v>38504</v>
+        <v>38565</v>
       </c>
       <c r="B244">
-        <v>54.35</v>
+        <v>63.98</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
-        <v>38473</v>
+        <v>38534</v>
       </c>
       <c r="B245">
-        <v>48.65</v>
+        <v>57.52</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
-        <v>38443</v>
+        <v>38504</v>
       </c>
       <c r="B246">
-        <v>51.88</v>
+        <v>54.35</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
-        <v>38412</v>
+        <v>38473</v>
       </c>
       <c r="B247">
-        <v>53.1</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
-        <v>38384</v>
+        <v>38443</v>
       </c>
       <c r="B248">
-        <v>45.48</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
-        <v>38353</v>
+        <v>38412</v>
       </c>
       <c r="B249">
-        <v>44.51</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
-        <v>38322</v>
+        <v>38384</v>
       </c>
       <c r="B250">
-        <v>39.6</v>
+        <v>45.48</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
-        <v>38292</v>
+        <v>38353</v>
       </c>
       <c r="B251">
-        <v>43.11</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
-        <v>38261</v>
+        <v>38322</v>
       </c>
       <c r="B252">
-        <v>49.78</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
-        <v>38231</v>
+        <v>38292</v>
       </c>
       <c r="B253">
-        <v>43.2</v>
+        <v>43.11</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
-        <v>38200</v>
+        <v>38261</v>
       </c>
       <c r="B254">
-        <v>42.74</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
-        <v>38169</v>
+        <v>38231</v>
       </c>
       <c r="B255">
-        <v>38.22</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
-        <v>38139</v>
+        <v>38200</v>
       </c>
       <c r="B256">
-        <v>35.18</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
-        <v>38108</v>
+        <v>38169</v>
       </c>
       <c r="B257">
-        <v>37.57</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
-        <v>38078</v>
+        <v>38139</v>
       </c>
       <c r="B258">
-        <v>33.590000000000003</v>
+        <v>35.18</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
-        <v>38047</v>
+        <v>38108</v>
       </c>
       <c r="B259">
-        <v>33.630000000000003</v>
+        <v>37.57</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
-        <v>38018</v>
+        <v>38078</v>
       </c>
       <c r="B260">
-        <v>30.86</v>
+        <v>33.590000000000003</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
-        <v>37987</v>
+        <v>38047</v>
       </c>
       <c r="B261">
-        <v>31.28</v>
+        <v>33.630000000000003</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
-        <v>37956</v>
+        <v>38018</v>
       </c>
       <c r="B262">
-        <v>29.81</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
-        <v>37926</v>
+        <v>37987</v>
       </c>
       <c r="B263">
-        <v>28.75</v>
+        <v>31.28</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
-        <v>37895</v>
+        <v>37956</v>
       </c>
       <c r="B264">
-        <v>29.61</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
-        <v>37865</v>
+        <v>37926</v>
       </c>
       <c r="B265">
-        <v>27.11</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
-        <v>37834</v>
+        <v>37895</v>
       </c>
       <c r="B266">
-        <v>29.89</v>
+        <v>29.61</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
-        <v>37803</v>
+        <v>37865</v>
       </c>
       <c r="B267">
-        <v>28.35</v>
+        <v>27.11</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
-        <v>37773</v>
+        <v>37834</v>
       </c>
       <c r="B268">
-        <v>27.65</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
-        <v>37742</v>
+        <v>37803</v>
       </c>
       <c r="B269">
-        <v>25.86</v>
+        <v>28.35</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
-        <v>37712</v>
+        <v>37773</v>
       </c>
       <c r="B270">
-        <v>25</v>
+        <v>27.65</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
-        <v>37681</v>
+        <v>37742</v>
       </c>
       <c r="B271">
-        <v>30.61</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
-        <v>37653</v>
+        <v>37712</v>
       </c>
       <c r="B272">
-        <v>32.770000000000003</v>
+        <v>25</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
-        <v>37622</v>
+        <v>37681</v>
       </c>
       <c r="B273">
-        <v>31.18</v>
+        <v>30.61</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
-        <v>37591</v>
+        <v>37653</v>
       </c>
       <c r="B274">
-        <v>28.33</v>
+        <v>32.770000000000003</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
-        <v>37561</v>
+        <v>37622</v>
       </c>
       <c r="B275">
-        <v>24.34</v>
+        <v>31.18</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
-        <v>37530</v>
+        <v>37591</v>
       </c>
       <c r="B276">
-        <v>27.54</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
-        <v>37500</v>
+        <v>37561</v>
       </c>
       <c r="B277">
-        <v>28.4</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
-        <v>37469</v>
+        <v>37530</v>
       </c>
       <c r="B278">
-        <v>26.65</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
-        <v>37438</v>
+        <v>37500</v>
       </c>
       <c r="B279">
-        <v>25.74</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
-        <v>37408</v>
+        <v>37469</v>
       </c>
       <c r="B280">
-        <v>24.08</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
-        <v>37377</v>
+        <v>37438</v>
       </c>
       <c r="B281">
-        <v>25.35</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
-        <v>37347</v>
+        <v>37408</v>
       </c>
       <c r="B282">
-        <v>25.73</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
-        <v>37316</v>
+        <v>37377</v>
       </c>
       <c r="B283">
-        <v>23.7</v>
+        <v>25.35</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
-        <v>37288</v>
+        <v>37347</v>
       </c>
       <c r="B284">
-        <v>20.28</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
-        <v>37257</v>
+        <v>37316</v>
       </c>
       <c r="B285">
-        <v>19.420000000000002</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
-        <v>37226</v>
+        <v>37288</v>
       </c>
       <c r="B286">
-        <v>18.71</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
-        <v>37196</v>
+        <v>37257</v>
       </c>
       <c r="B287">
-        <v>18.8</v>
+        <v>19.420000000000002</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
-        <v>37165</v>
+        <v>37226</v>
       </c>
       <c r="B288">
-        <v>20.54</v>
+        <v>18.71</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
-        <v>37135</v>
+        <v>37196</v>
       </c>
       <c r="B289">
-        <v>25.62</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
-        <v>37104</v>
+        <v>37165</v>
       </c>
       <c r="B290">
-        <v>25.68</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
-        <v>37073</v>
+        <v>37135</v>
       </c>
       <c r="B291">
-        <v>24.61</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
-        <v>37043</v>
+        <v>37104</v>
       </c>
       <c r="B292">
-        <v>27.85</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
-        <v>37012</v>
+        <v>37073</v>
       </c>
       <c r="B293">
-        <v>28.31</v>
+        <v>24.61</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
-        <v>36982</v>
+        <v>37043</v>
       </c>
       <c r="B294">
-        <v>25.66</v>
+        <v>27.85</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
-        <v>36951</v>
+        <v>37012</v>
       </c>
       <c r="B295">
-        <v>24.5</v>
+        <v>28.31</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
-        <v>36923</v>
+        <v>36982</v>
       </c>
       <c r="B296">
-        <v>27.5</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
-        <v>36892</v>
+        <v>36951</v>
       </c>
       <c r="B297">
-        <v>25.62</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
-        <v>36861</v>
+        <v>36923</v>
       </c>
       <c r="B298">
-        <v>25.66</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
-        <v>36831</v>
+        <v>36892</v>
       </c>
       <c r="B299">
-        <v>32.549999999999997</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
-        <v>36800</v>
+        <v>36861</v>
       </c>
       <c r="B300">
-        <v>30.96</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
-        <v>36770</v>
+        <v>36831</v>
       </c>
       <c r="B301">
-        <v>33.14</v>
+        <v>32.549999999999997</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
-        <v>36739</v>
+        <v>36800</v>
       </c>
       <c r="B302">
-        <v>30.2</v>
+        <v>30.96</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
-        <v>36708</v>
+        <v>36770</v>
       </c>
       <c r="B303">
-        <v>28.68</v>
+        <v>33.14</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
-        <v>36678</v>
+        <v>36739</v>
       </c>
       <c r="B304">
-        <v>29.8</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
-        <v>36647</v>
+        <v>36708</v>
       </c>
       <c r="B305">
-        <v>27.74</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
-        <v>36617</v>
+        <v>36678</v>
       </c>
       <c r="B306">
-        <v>22.76</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
-        <v>36586</v>
+        <v>36647</v>
       </c>
       <c r="B307">
-        <v>27.49</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
-        <v>36557</v>
+        <v>36617</v>
       </c>
       <c r="B308">
-        <v>27.78</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
-        <v>36526</v>
+        <v>36586</v>
       </c>
       <c r="B309">
-        <v>25.51</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
-        <v>36495</v>
+        <v>36557</v>
       </c>
       <c r="B310">
-        <v>25.47</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
-        <v>36465</v>
+        <v>36526</v>
       </c>
       <c r="B311">
-        <v>24.58</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
-        <v>36434</v>
+        <v>36495</v>
       </c>
       <c r="B312">
-        <v>22</v>
+        <v>25.47</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
-        <v>36404</v>
+        <v>36465</v>
       </c>
       <c r="B313">
-        <v>22.54</v>
+        <v>24.58</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" s="1">
-        <v>36373</v>
+        <v>36434</v>
       </c>
       <c r="B314">
-        <v>20.22</v>
+        <v>22</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" s="1">
-        <v>36342</v>
+        <v>36404</v>
       </c>
       <c r="B315">
-        <v>19.079999999999998</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
-        <v>36312</v>
+        <v>36373</v>
       </c>
       <c r="B316">
-        <v>15.86</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
-        <v>36281</v>
+        <v>36342</v>
       </c>
       <c r="B317">
-        <v>15.23</v>
+        <v>19.079999999999998</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
-        <v>36251</v>
+        <v>36312</v>
       </c>
       <c r="B318">
-        <v>15.29</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
-        <v>36220</v>
+        <v>36281</v>
       </c>
       <c r="B319">
-        <v>12.51</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
-        <v>36192</v>
+        <v>36251</v>
       </c>
       <c r="B320">
-        <v>10.27</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
-        <v>36161</v>
+        <v>36220</v>
       </c>
       <c r="B321">
-        <v>11.11</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
-        <v>36130</v>
+        <v>36192</v>
       </c>
       <c r="B322">
-        <v>9.82</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
-        <v>36100</v>
+        <v>36161</v>
       </c>
       <c r="B323">
-        <v>11.04</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
-        <v>36069</v>
+        <v>36130</v>
       </c>
       <c r="B324">
-        <v>12.7</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
-        <v>36039</v>
+        <v>36100</v>
       </c>
       <c r="B325">
-        <v>13.34</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
-        <v>36008</v>
+        <v>36069</v>
       </c>
       <c r="B326">
-        <v>11.91</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
-        <v>35977</v>
+        <v>36039</v>
       </c>
       <c r="B327">
-        <v>12.08</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
-        <v>35947</v>
+        <v>36008</v>
       </c>
       <c r="B328">
-        <v>12.21</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
-        <v>35916</v>
+        <v>35977</v>
       </c>
       <c r="B329">
-        <v>14.36</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
-        <v>35886</v>
+        <v>35947</v>
       </c>
       <c r="B330">
-        <v>13.53</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
-        <v>35855</v>
+        <v>35916</v>
       </c>
       <c r="B331">
-        <v>13.1</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
-        <v>35827</v>
+        <v>35886</v>
       </c>
       <c r="B332">
-        <v>14.07</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
-        <v>35796</v>
+        <v>35855</v>
       </c>
       <c r="B333">
-        <v>15.19</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
-        <v>35765</v>
+        <v>35827</v>
       </c>
       <c r="B334">
-        <v>17.18</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
-        <v>35735</v>
+        <v>35796</v>
       </c>
       <c r="B335">
-        <v>19.170000000000002</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
-        <v>35704</v>
+        <v>35765</v>
       </c>
       <c r="B336">
-        <v>19.87</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
-        <v>35674</v>
+        <v>35735</v>
       </c>
       <c r="B337">
-        <v>18.46</v>
+        <v>19.170000000000002</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
-        <v>35643</v>
+        <v>35704</v>
       </c>
       <c r="B338">
-        <v>18.600000000000001</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
-        <v>35612</v>
+        <v>35674</v>
       </c>
       <c r="B339">
         <v>18.46</v>
@@ -3604,977 +3604,993 @@
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
-        <v>35582</v>
+        <v>35643</v>
       </c>
       <c r="B340">
-        <v>17.579999999999998</v>
+        <v>18.600000000000001</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
-        <v>35551</v>
+        <v>35612</v>
       </c>
       <c r="B341">
-        <v>19.02</v>
+        <v>18.46</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
-        <v>35521</v>
+        <v>35582</v>
       </c>
       <c r="B342">
-        <v>17.559999999999999</v>
+        <v>17.579999999999998</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
-        <v>35490</v>
+        <v>35551</v>
       </c>
       <c r="B343">
-        <v>19.13</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
-        <v>35462</v>
+        <v>35521</v>
       </c>
       <c r="B344">
-        <v>20.85</v>
+        <v>17.559999999999999</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
-        <v>35431</v>
+        <v>35490</v>
       </c>
       <c r="B345">
-        <v>23.54</v>
+        <v>19.13</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
-        <v>35400</v>
+        <v>35462</v>
       </c>
       <c r="B346">
-        <v>23.78</v>
+        <v>20.85</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
-        <v>35370</v>
+        <v>35431</v>
       </c>
       <c r="B347">
-        <v>22.76</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
-        <v>35339</v>
+        <v>35400</v>
       </c>
       <c r="B348">
-        <v>24.16</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
-        <v>35309</v>
+        <v>35370</v>
       </c>
       <c r="B349">
-        <v>22.63</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
-        <v>35278</v>
+        <v>35339</v>
       </c>
       <c r="B350">
-        <v>20.51</v>
+        <v>24.16</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
-        <v>35247</v>
+        <v>35309</v>
       </c>
       <c r="B351">
-        <v>19.57</v>
+        <v>22.63</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
-        <v>35217</v>
+        <v>35278</v>
       </c>
       <c r="B352">
-        <v>18.46</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
-        <v>35186</v>
+        <v>35247</v>
       </c>
       <c r="B353">
-        <v>19.149999999999999</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
-        <v>35156</v>
+        <v>35217</v>
       </c>
       <c r="B354">
-        <v>20.9</v>
+        <v>18.46</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
-        <v>35125</v>
+        <v>35186</v>
       </c>
       <c r="B355">
-        <v>19.850000000000001</v>
+        <v>19.149999999999999</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
-        <v>35096</v>
+        <v>35156</v>
       </c>
       <c r="B356">
-        <v>18</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
-        <v>35065</v>
+        <v>35125</v>
       </c>
       <c r="B357">
-        <v>17.850000000000001</v>
+        <v>19.850000000000001</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
-        <v>35034</v>
+        <v>35096</v>
       </c>
       <c r="B358">
-        <v>17.93</v>
+        <v>18</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
-        <v>35004</v>
+        <v>35065</v>
       </c>
       <c r="B359">
-        <v>16.86</v>
+        <v>17.850000000000001</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
-        <v>34973</v>
+        <v>35034</v>
       </c>
       <c r="B360">
-        <v>16.11</v>
+        <v>17.93</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
-        <v>34943</v>
+        <v>35004</v>
       </c>
       <c r="B361">
-        <v>16.7</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
-        <v>34912</v>
+        <v>34973</v>
       </c>
       <c r="B362">
-        <v>16.100000000000001</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
-        <v>34881</v>
+        <v>34943</v>
       </c>
       <c r="B363">
-        <v>15.85</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
-        <v>34851</v>
+        <v>34912</v>
       </c>
       <c r="B364">
-        <v>17.309999999999999</v>
+        <v>16.100000000000001</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
-        <v>34820</v>
+        <v>34881</v>
       </c>
       <c r="B365">
-        <v>18.350000000000001</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
-        <v>34790</v>
+        <v>34851</v>
       </c>
       <c r="B366">
-        <v>18.649999999999999</v>
+        <v>17.309999999999999</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
-        <v>34759</v>
+        <v>34820</v>
       </c>
       <c r="B367">
-        <v>17.010000000000002</v>
+        <v>18.350000000000001</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
-        <v>34731</v>
+        <v>34790</v>
       </c>
       <c r="B368">
-        <v>17.11</v>
+        <v>18.649999999999999</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
-        <v>34700</v>
+        <v>34759</v>
       </c>
       <c r="B369">
-        <v>16.55</v>
+        <v>17.010000000000002</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
-        <v>34669</v>
+        <v>34731</v>
       </c>
       <c r="B370">
-        <v>15.93</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
-        <v>34639</v>
+        <v>34700</v>
       </c>
       <c r="B371">
-        <v>17.190000000000001</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
-        <v>34608</v>
+        <v>34669</v>
       </c>
       <c r="B372">
-        <v>16.489999999999998</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
-        <v>34578</v>
+        <v>34639</v>
       </c>
       <c r="B373">
-        <v>15.9</v>
+        <v>17.190000000000001</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
-        <v>34547</v>
+        <v>34608</v>
       </c>
       <c r="B374">
-        <v>16.89</v>
+        <v>16.489999999999998</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
-        <v>34516</v>
+        <v>34578</v>
       </c>
       <c r="B375">
-        <v>17.600000000000001</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
-        <v>34486</v>
+        <v>34547</v>
       </c>
       <c r="B376">
-        <v>16.760000000000002</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
-        <v>34455</v>
+        <v>34516</v>
       </c>
       <c r="B377">
-        <v>16.190000000000001</v>
+        <v>17.600000000000001</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
-        <v>34425</v>
+        <v>34486</v>
       </c>
       <c r="B378">
-        <v>15.23</v>
+        <v>16.760000000000002</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
-        <v>34394</v>
+        <v>34455</v>
       </c>
       <c r="B379">
-        <v>13.82</v>
+        <v>16.190000000000001</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
-        <v>34366</v>
+        <v>34425</v>
       </c>
       <c r="B380">
-        <v>13.8</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
-        <v>34335</v>
+        <v>34394</v>
       </c>
       <c r="B381">
-        <v>14.29</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
-        <v>34304</v>
+        <v>34366</v>
       </c>
       <c r="B382">
-        <v>13.73</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
-        <v>34274</v>
+        <v>34335</v>
       </c>
       <c r="B383">
-        <v>15.2</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
-        <v>34243</v>
+        <v>34304</v>
       </c>
       <c r="B384">
-        <v>16.61</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
-        <v>34213</v>
+        <v>34274</v>
       </c>
       <c r="B385">
-        <v>16.010000000000002</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
-        <v>34182</v>
+        <v>34243</v>
       </c>
       <c r="B386">
-        <v>16.7</v>
+        <v>16.61</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
-        <v>34151</v>
+        <v>34213</v>
       </c>
       <c r="B387">
-        <v>16.78</v>
+        <v>16.010000000000002</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
-        <v>34121</v>
+        <v>34182</v>
       </c>
       <c r="B388">
-        <v>17.649999999999999</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
-        <v>34090</v>
+        <v>34151</v>
       </c>
       <c r="B389">
-        <v>18.510000000000002</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
-        <v>34060</v>
+        <v>34121</v>
       </c>
       <c r="B390">
-        <v>18.670000000000002</v>
+        <v>17.649999999999999</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
-        <v>34029</v>
+        <v>34090</v>
       </c>
       <c r="B391">
-        <v>18.79</v>
+        <v>18.510000000000002</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
-        <v>34001</v>
+        <v>34060</v>
       </c>
       <c r="B392">
-        <v>18.47</v>
+        <v>18.670000000000002</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
-        <v>33970</v>
+        <v>34029</v>
       </c>
       <c r="B393">
-        <v>17.39</v>
+        <v>18.79</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
-        <v>33939</v>
+        <v>34001</v>
       </c>
       <c r="B394">
-        <v>18.14</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
-        <v>33909</v>
+        <v>33970</v>
       </c>
       <c r="B395">
-        <v>19.21</v>
+        <v>17.39</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
-        <v>33878</v>
+        <v>33939</v>
       </c>
       <c r="B396">
-        <v>20.260000000000002</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
-        <v>33848</v>
+        <v>33909</v>
       </c>
       <c r="B397">
-        <v>20.27</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
-        <v>33817</v>
+        <v>33878</v>
       </c>
       <c r="B398">
-        <v>19.739999999999998</v>
+        <v>20.260000000000002</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
-        <v>33786</v>
+        <v>33848</v>
       </c>
       <c r="B399">
-        <v>20.239999999999998</v>
+        <v>20.27</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
-        <v>33756</v>
+        <v>33817</v>
       </c>
       <c r="B400">
-        <v>21.16</v>
+        <v>19.739999999999998</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
-        <v>33725</v>
+        <v>33786</v>
       </c>
       <c r="B401">
-        <v>19.89</v>
+        <v>20.239999999999998</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
-        <v>33695</v>
+        <v>33756</v>
       </c>
       <c r="B402">
-        <v>18.920000000000002</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
-        <v>33664</v>
+        <v>33725</v>
       </c>
       <c r="B403">
-        <v>17.63</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
-        <v>33635</v>
+        <v>33695</v>
       </c>
       <c r="B404">
-        <v>18.05</v>
+        <v>18.920000000000002</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
-        <v>33604</v>
+        <v>33664</v>
       </c>
       <c r="B405">
-        <v>18.16</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
-        <v>33573</v>
+        <v>33635</v>
       </c>
       <c r="B406">
-        <v>18.41</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
-        <v>33543</v>
+        <v>33604</v>
       </c>
       <c r="B407">
-        <v>21.11</v>
+        <v>18.16</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
-        <v>33512</v>
+        <v>33573</v>
       </c>
       <c r="B408">
-        <v>22.21</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
-        <v>33482</v>
+        <v>33543</v>
       </c>
       <c r="B409">
-        <v>20.5</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
-        <v>33451</v>
+        <v>33512</v>
       </c>
       <c r="B410">
-        <v>19.77</v>
+        <v>22.21</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
-        <v>33420</v>
+        <v>33482</v>
       </c>
       <c r="B411">
-        <v>19.399999999999999</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
-        <v>33390</v>
+        <v>33451</v>
       </c>
       <c r="B412">
-        <v>18.170000000000002</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
-        <v>33359</v>
+        <v>33420</v>
       </c>
       <c r="B413">
-        <v>19.190000000000001</v>
+        <v>19.399999999999999</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
-        <v>33329</v>
+        <v>33390</v>
       </c>
       <c r="B414">
-        <v>19.18</v>
+        <v>18.170000000000002</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
-        <v>33298</v>
+        <v>33359</v>
       </c>
       <c r="B415">
-        <v>19.079999999999998</v>
+        <v>19.190000000000001</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A416" s="1">
-        <v>33270</v>
+        <v>33329</v>
       </c>
       <c r="B416">
-        <v>19.54</v>
+        <v>19.18</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" s="1">
-        <v>33239</v>
+        <v>33298</v>
       </c>
       <c r="B417">
-        <v>23.57</v>
+        <v>19.079999999999998</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A418" s="1">
-        <v>33208</v>
+        <v>33270</v>
       </c>
       <c r="B418">
-        <v>28.27</v>
+        <v>19.54</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A419" s="1">
-        <v>33178</v>
+        <v>33239</v>
       </c>
       <c r="B419">
-        <v>33.07</v>
+        <v>23.57</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A420" s="1">
-        <v>33147</v>
+        <v>33208</v>
       </c>
       <c r="B420">
-        <v>36.020000000000003</v>
+        <v>28.27</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A421" s="1">
-        <v>33117</v>
+        <v>33178</v>
       </c>
       <c r="B421">
-        <v>34.9</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A422" s="1">
-        <v>33086</v>
+        <v>33147</v>
       </c>
       <c r="B422">
-        <v>27.17</v>
+        <v>36.020000000000003</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A423" s="1">
-        <v>33055</v>
+        <v>33117</v>
       </c>
       <c r="B423">
-        <v>17.170000000000002</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A424" s="1">
-        <v>33025</v>
+        <v>33086</v>
       </c>
       <c r="B424">
-        <v>15.1</v>
+        <v>27.17</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A425" s="1">
-        <v>32994</v>
+        <v>33055</v>
       </c>
       <c r="B425">
-        <v>16.350000000000001</v>
+        <v>17.170000000000002</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A426" s="1">
-        <v>32964</v>
+        <v>33025</v>
       </c>
       <c r="B426">
-        <v>16.61</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A427" s="1">
-        <v>32933</v>
+        <v>32994</v>
       </c>
       <c r="B427">
-        <v>18.39</v>
+        <v>16.350000000000001</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A428" s="1">
-        <v>32905</v>
+        <v>32964</v>
       </c>
       <c r="B428">
-        <v>19.809999999999999</v>
+        <v>16.61</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A429" s="1">
-        <v>32874</v>
+        <v>32933</v>
       </c>
       <c r="B429">
-        <v>21.25</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A430" s="1">
-        <v>32843</v>
+        <v>32905</v>
       </c>
       <c r="B430">
-        <v>19.84</v>
+        <v>19.809999999999999</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A431" s="1">
-        <v>32813</v>
+        <v>32874</v>
       </c>
       <c r="B431">
-        <v>18.73</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A432" s="1">
-        <v>32782</v>
+        <v>32843</v>
       </c>
       <c r="B432">
-        <v>18.91</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A433" s="1">
-        <v>32752</v>
+        <v>32813</v>
       </c>
       <c r="B433">
-        <v>17.77</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A434" s="1">
-        <v>32721</v>
+        <v>32782</v>
       </c>
       <c r="B434">
-        <v>16.77</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A435" s="1">
-        <v>32690</v>
+        <v>32752</v>
       </c>
       <c r="B435">
-        <v>17.62</v>
+        <v>17.77</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A436" s="1">
-        <v>32660</v>
+        <v>32721</v>
       </c>
       <c r="B436">
-        <v>17.670000000000002</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A437" s="1">
-        <v>32629</v>
+        <v>32690</v>
       </c>
       <c r="B437">
-        <v>18.63</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A438" s="1">
-        <v>32599</v>
+        <v>32660</v>
       </c>
       <c r="B438">
-        <v>20.32</v>
+        <v>17.670000000000002</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A439" s="1">
-        <v>32568</v>
+        <v>32629</v>
       </c>
       <c r="B439">
-        <v>18.7</v>
+        <v>18.63</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A440" s="1">
-        <v>32540</v>
+        <v>32599</v>
       </c>
       <c r="B440">
-        <v>16.89</v>
+        <v>20.32</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A441" s="1">
-        <v>32509</v>
+        <v>32568</v>
       </c>
       <c r="B441">
-        <v>17.170000000000002</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A442" s="1">
-        <v>32478</v>
+        <v>32540</v>
       </c>
       <c r="B442">
-        <v>15.31</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A443" s="1">
-        <v>32448</v>
+        <v>32509</v>
       </c>
       <c r="B443">
-        <v>13.02</v>
+        <v>17.170000000000002</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A444" s="1">
-        <v>32417</v>
+        <v>32478</v>
       </c>
       <c r="B444">
-        <v>12.41</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A445" s="1">
-        <v>32387</v>
+        <v>32448</v>
       </c>
       <c r="B445">
-        <v>13.18</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A446" s="1">
-        <v>32356</v>
+        <v>32417</v>
       </c>
       <c r="B446">
-        <v>14.89</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A447" s="1">
-        <v>32325</v>
+        <v>32387</v>
       </c>
       <c r="B447">
-        <v>14.91</v>
+        <v>13.18</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A448" s="1">
-        <v>32295</v>
+        <v>32356</v>
       </c>
       <c r="B448">
-        <v>15.54</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A449" s="1">
-        <v>32264</v>
+        <v>32325</v>
       </c>
       <c r="B449">
-        <v>16.309999999999999</v>
+        <v>14.91</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A450" s="1">
-        <v>32234</v>
+        <v>32295</v>
       </c>
       <c r="B450">
-        <v>16.600000000000001</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A451" s="1">
-        <v>32203</v>
+        <v>32264</v>
       </c>
       <c r="B451">
-        <v>14.73</v>
+        <v>16.309999999999999</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A452" s="1">
-        <v>32174</v>
+        <v>32234</v>
       </c>
       <c r="B452">
-        <v>15.73</v>
+        <v>16.600000000000001</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A453" s="1">
-        <v>32143</v>
+        <v>32203</v>
       </c>
       <c r="B453">
-        <v>16.75</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A454" s="1">
-        <v>32112</v>
+        <v>32174</v>
       </c>
       <c r="B454">
-        <v>17.05</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A455" s="1">
-        <v>32082</v>
+        <v>32143</v>
       </c>
       <c r="B455">
-        <v>17.78</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A456" s="1">
-        <v>32051</v>
+        <v>32112</v>
       </c>
       <c r="B456">
-        <v>18.760000000000002</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A457" s="1">
-        <v>32021</v>
+        <v>32082</v>
       </c>
       <c r="B457">
-        <v>18.309999999999999</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A458" s="1">
-        <v>31990</v>
+        <v>32051</v>
       </c>
       <c r="B458">
-        <v>18.98</v>
+        <v>18.760000000000002</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A459" s="1">
-        <v>31959</v>
+        <v>32021</v>
       </c>
       <c r="B459">
-        <v>19.86</v>
+        <v>18.309999999999999</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A460" s="1">
-        <v>31929</v>
+        <v>31990</v>
       </c>
       <c r="B460">
-        <v>18.86</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A461" s="1">
+        <v>31959</v>
+      </c>
+      <c r="B461">
+        <v>19.86</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A462" s="1">
+        <v>31929</v>
+      </c>
+      <c r="B462">
+        <v>18.86</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A463" s="1">
         <v>31898</v>
       </c>
-      <c r="B461">
+      <c r="B463">
         <v>18.579999999999998</v>
       </c>
     </row>
